--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_932_Denmark_North_Sea.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_932_Denmark_North_Sea.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R0b5be370f01f405b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R7f8db2fbdf344790"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R45d1ada7b9d64b7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R63c2224d0b4c476d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9bf7da814bad4b77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R55beee9279cb4634"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rf0b7001ce93745da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rb6fb418bb5144d72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R2e2f18e903114d85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R2924ac61f2e741d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R8d572293deb744ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rb766f28d553d48e5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ932CommercialTable" displayName="EEZ932CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ932CommercialTable" displayName="EEZ932CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ932FunctionalTable" displayName="EEZ932FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ932FunctionalTable" displayName="EEZ932FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ932ValidationTable" displayName="EEZ932ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ932ValidationTable" displayName="EEZ932ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -13491,7 +13445,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6db7170e9da4b6a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bce620a1b9a4678"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13501,20 +13455,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -13522,714 +13466,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>6.1616159614</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>6.1616159614</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$192,A2,'Species'!$U$2:$U$192))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>793.7698999978807</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>793.7698999978807</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>9527.7785507639</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.123939392131572</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1330.2687596670455</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>9527.7785507639</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1542.13207155144</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$192,A3,'Species'!$U$2:$U$192))</x:f>
-        <x:v>14693092.87377291</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.123939392131572</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1330.2687596670455</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>12674506.155106973</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>2018586.718665937</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.159263540051427</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.15926354005142696</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>9594.7598405133</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.016925439295007</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>103.97416451974863</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>9594.7598405133</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>111.63368322882926</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$192,A4,'Species'!$U$2:$U$192))</x:f>
-        <x:v>1071098.380692554</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.016925439295007</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>103.97416451974863</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>997607.1381850069</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>73491.24250754702</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0736675187000497</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.07366751870004966</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>26211.3208714841</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.3003089642759766</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>199.66822826080093</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>26211.3208714841</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>251.57635754438354</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$192,A5,'Species'!$U$2:$U$192))</x:f>
-        <x:v>6594148.631275047</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.3003089642759766</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>199.66822826080093</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>5233567.998784582</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1360580.6324904645</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.2599719030700354</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.25997190307003537</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>54144.677472687305</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.1993496114068902</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>158.25214722707594</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>54144.677472687305</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>172.71638271049653</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$192,A6,'Species'!$U$2:$U$192))</x:f>
-        <x:v>9351672.83610906</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.1993496114068902</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>158.25214722707594</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>8568511.470970253</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>783161.3651388083</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0913999319242467</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.09139993192424672</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>11805.8453733136</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.0154247341844265</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>10.361550170453654</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>11805.8453733136</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>14.471847453808993</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$192,A7,'Species'!$U$2:$U$192))</x:f>
-        <x:v>170852.3933058511</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.0154247341844265</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>10.361550170453654</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>122326.85914020702</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>48525.53416564407</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.396687485534356</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.39668748553435595</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>21467.1467666003</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.334850104224548</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>216.1972195038243</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>21467.1467666003</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>316.28785080682246</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$192,A8,'Species'!$U$2:$U$192))</x:f>
-        <x:v>6789797.713762637</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.334850104224548</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>216.1972195038243</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>4641137.441619498</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>2148660.2721431395</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4629598453333839</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.46295984533338386</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>2370.7548301218</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6962728190260234</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>496.9043732987936</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>2370.7548301218</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>579.5093061868469</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$192,A9,'Species'!$U$2:$U$192))</x:f>
-        <x:v>1373874.486743</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6962728190260234</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>496.9043732987936</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1178038.4431067607</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>195836.04363623937</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1662390941332732</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.16623909413327317</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>149.26900081100004</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.372066473544144</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>235.5409777663262</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>149.26900081100004</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>263.01307630524866</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$192,A10,'Species'!$U$2:$U$192))</x:f>
-        <x:v>39259.69910031178</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.372066473544144</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>235.5409777663262</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>35158.96640122549</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>4100.732699086293</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1166340515329642</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.11663405153296427</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1037.4942458064</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.877074874723498</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>753.4854575146002</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1037.4942458064</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>764.8211873797046</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$192,A11,'Species'!$U$2:$U$192))</x:f>
-        <x:v>793497.5809772619</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.877074874723498</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>753.4854575146002</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>781736.8264702003</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>11760.75450706156</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.015044391039073</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.01504439103907289</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>507.42670565699996</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.965669541734436</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>923.9948310683782</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>507.42670565699996</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1023.0286830296733</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$192,A12,'Species'!$U$2:$U$192))</x:f>
-        <x:v>519112.07442236634</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.965669541734436</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>923.9948310683782</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>468859.6531731233</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>50252.42124924302</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1071800930388174</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.10718009303881743</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>0.1613044228</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.45</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2818.382931264455</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>0.1613044228</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2818.382931264455</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$192,A13,'Species'!$U$2:$U$192))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>454.617631956985</x:v>
       </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.45</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2818.382931264455</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>454.617631956985</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02836b611480410b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2daae4d5d144100"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14239,20 +13719,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -14260,1416 +13730,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>139.59209903019996</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.9667364390285345</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>926.267527352873</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>139.59209903019996</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1047.7965478076324</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$192,A2,'Species'!$U$2:$U$192))</x:f>
-        <x:v>146264.11946506466</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.9667364390285345</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>926.267527352873</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>129299.62840670069</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>16964.491058363972</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1312029374516348</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.1312029374516348</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>829.007529206</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.448172442913583</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2806.547797188428</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>829.007529206</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2807.7892828368776</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$192,A3,'Species'!$U$2:$U$192))</x:f>
-        <x:v>2327678.4558956865</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.448172442913583</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2806.547797188428</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2326649.2549457205</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1029.2009499659762</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0004423532888673</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0004423532888673359</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1.4143920861</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.54280439767373</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>348.98310122913847</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1.4143920861</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>350.5319461299276</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$192,A4,'Species'!$U$2:$U$192))</x:f>
-        <x:v>495.789610531401</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.54280439767373</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>348.98310122913847</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>493.5989365611286</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>2.190673970272428</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0044381659035466</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.004438165903546531</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>4394.316073076401</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.09941672609632</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1257.2357622696636</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>4394.316073076401</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1265.650392958333</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$192,A5,'Species'!$U$2:$U$192))</x:f>
-        <x:v>5561667.864672266</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.09941672609632</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1257.2357622696636</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>5524691.317788044</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>36976.546884221956</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.006692961607677</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.006692961607677022</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>2325.0134104343</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.2804344970774775</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1907.368021503896</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>2325.0134104343</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2079.3768641312254</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$192,A6,'Species'!$U$2:$U$192))</x:f>
-        <x:v>4834579.09445192</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.2804344970774775</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1907.368021503896</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>4434656.228630097</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>399922.8658218235</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0901812553676484</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.09018125536764844</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>16578.2375842455</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.298414563793921</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>198.79916859823493</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>16578.2375842455</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>254.09575459666485</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$192,A7,'Species'!$U$2:$U$192))</x:f>
-        <x:v>4212459.78885165</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.298414563793921</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>198.79916859823493</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>3295739.848572016</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>916719.9402796342</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.278153004302458</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.278153004302458</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>123.6973569874</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.3632902610287574</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>230.82894201779922</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>123.6973569874</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>234.84716183980314</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$192,A8,'Species'!$U$2:$U$192))</x:f>
-        <x:v>29049.973215575832</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.3632902610287574</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>230.82894201779922</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>28552.930043799566</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>497.0431717762658</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.017407781653715</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.017407781653715135</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>127.19369975000001</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.8379325316349164</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>688.5453213821825</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>127.19369975000001</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>782.8460786161578</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$192,A9,'Species'!$U$2:$U$192))</x:f>
-        <x:v>99573.08907396847</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.8379325316349164</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>688.5453213821825</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>87578.62687215257</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>11994.462201815899</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1369564998926671</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.13695649989266714</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>112.39638463480001</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.313970947988053</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>206.0492072599541</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>112.39638463480001</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>217.81457672785425</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$192,A10,'Species'!$U$2:$U$192))</x:f>
-        <x:v>24481.570944970066</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.313970947988053</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>206.0492072599541</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>23159.18595288543</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1322.384992084637</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0570998045775386</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.05709980457753868</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>195.2127901821</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.113640738063777</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1299.0944819583847</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>195.2127901821</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1335.1483887465859</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$192,A11,'Species'!$U$2:$U$192))</x:f>
-        <x:v>260638.04227435615</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.113640738063777</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1299.0944819583847</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>253599.85853326606</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>7038.183741090092</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0277531059433413</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.02775310594334127</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>5579.2939215935985</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.9232137789168005</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>83.79416524990928</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>5579.2939215935985</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>89.76726721425999</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$192,A12,'Species'!$U$2:$U$192))</x:f>
-        <x:v>500837.9683265891</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.9232137789168005</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>83.79416524990928</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>467512.2768438284</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>33325.69148276071</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0712830296302425</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.07128302963024241</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>90.46453239130001</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.450347364254712</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2820.638076456075</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>90.46453239130001</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2861.0589258177506</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$192,A13,'Species'!$U$2:$U$192))</x:f>
-        <x:v>258824.3578680579</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.450347364254712</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2820.638076456075</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>255167.70463169474</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>3656.6532363631704</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0143303920127398</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.014330392012739735</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>0.100442343</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>0.100442343</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$192,A14,'Species'!$U$2:$U$192))</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>120.7582567185433</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
-        <x:v>120.7582567185433</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>2420.5968061242</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.9906303014760773</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>978.6565372928275</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>2420.5968061242</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>1543.7983414066312</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$192,A15,'Species'!$U$2:$U$192))</x:f>
-        <x:v>3736913.334508729</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.9906303014760773</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>978.6565372928275</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>2368932.8884635875</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>1367980.4460451417</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.5774669483914208</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.5774669483914207</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>21621.035558460895</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.3394332173081436</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>218.49083142832978</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>21621.035558460895</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>257.8824542406073</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$192,A16,'Species'!$U$2:$U$192))</x:f>
-        <x:v>5575685.713039335</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.3394332173081436</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>218.49083142832978</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>4723998.035509603</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>851687.6775297318</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.1802895918092513</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.1802895918092514</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>29750.582299327394</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.402425282014673</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>252.59530963605434</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>29750.582299327394</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>262.0502848561858</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$192,A17,'Species'!$U$2:$U$192))</x:f>
-        <x:v>7796148.566176142</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.402425282014673</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>252.59530963605434</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>7514857.547751521</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>281291.01842462085</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0374313174451038</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.037431317445103716</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>10.4067960156</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.2171188473555112</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>164.8613483017899</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>10.4067960156</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>167.34093818046568</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$192,A18,'Species'!$U$2:$U$192))</x:f>
-        <x:v>1741.4830087032362</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.2171188473555112</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>164.8613483017899</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>1715.6784226335108</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>25.804586069725474</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0150404561421926</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.015040456142192586</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>12230.296490106199</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.0469361284062377</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>11.141306665904324</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>12230.296490106199</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>17.099263887944208</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$192,A19,'Species'!$U$2:$U$192))</x:f>
-        <x:v>209129.0671121237</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.0469361284062377</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>11.141306665904324</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>136261.48381120645</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>72867.58330091726</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.5347628784218807</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.5347628784218807</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>4015.4659189197</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.147133217841224</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>140.3244077238433</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>4015.4659189197</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>142.0160011019057</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$192,A20,'Species'!$U$2:$U$192))</x:f>
-        <x:v>570260.4123659648</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.147133217841224</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>140.3244077238433</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>563467.8768076851</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>6792.53555827972</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0120548763077013</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.012054876307701303</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>0.0578147584</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.31</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>204.17379446695296</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>0.0578147584</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$192,A21,'Species'!$U$2:$U$192))</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>11.804258598718143</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.31</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
-        <x:v>11.804258598718143</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>26453.502062981595</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.010183894300901</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>102.37263793099828</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>26453.502062981595</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>102.38059433205065</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$192,A22,'Species'!$U$2:$U$192))</x:f>
-        <x:v>2708325.263372184</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.010183894300901</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>102.37263793099828</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>2708114.788700531</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>210.47467165300623</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.000077719996409</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.00007771999640901521</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>6.8091125247</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.493730834504915</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>311.69571686538507</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>6.8091125247</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>319.9764196105429</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$192,A23,'Species'!$U$2:$U$192))</x:f>
-        <x:v>2178.75544637881</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.493730834504915</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>311.69571686538507</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>2122.3712096034383</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>56.384236775371846</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0265666234635302</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.02656662346353028</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>9633.083287238598</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.3035691687541044</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>201.17275743866776</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>9633.083287238598</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>247.2405533520646</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$192,A24,'Species'!$U$2:$U$192))</x:f>
-        <x:v>2381688.8424233967</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.3035691687541044</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>201.17275743866776</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>1937913.9275301348</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>443774.91489326186</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.2289961946136851</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.22899619461368523</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>155.1134020964</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.9083026982856555</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>809.6600263364851</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>155.1134020964</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>890.5975744750125</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$192,A25,'Species'!$U$2:$U$192))</x:f>
-        <x:v>138143.61967562116</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.9083026982856555</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>809.6600263364851</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>125589.12122651302</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>12554.498449108141</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.09996485624312</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.09996485624311997</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>29.9068136285</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.840609046020625</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>692.8018616551041</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>29.9068136285</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>694.0666985211565</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$192,A26,'Species'!$U$2:$U$192))</x:f>
-        <x:v>20757.32339842052</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.840609046020625</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>692.8018616551041</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>20719.496157997037</x:v>
       </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>37.82724042348491</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.0018256834111714</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.001825683411171408</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0733240a23434995"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb38bd2e964d48f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15844,7 +14395,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -15943,7 +14494,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>41397655.057692945</x:v>
+        <x:v>34702699.34048979</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15957,7 +14508,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>41397655.05769295</x:v>
+        <x:v>36930926.23826311</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15971,7 +14522,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-7.450580596923828e-9</x:v>
+        <x:v>-6694955.717203163</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15985,7 +14536,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-4466728.819429845</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15996,9 +14547,9 @@
         <x:v>EEZ_932</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -16010,47 +14561,19 @@
         <x:v>EEZ_932</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_932</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_932</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fa4506386b945e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fd328491e544aa9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16097,7 +14620,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
